--- a/港岛-薄扶林-碧丽轩/碧丽轩_销控明细表.xlsx
+++ b/港岛-薄扶林-碧丽轩/碧丽轩_销控明细表.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="低座" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="独立屋销控表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="独立屋销控表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="低座" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2171,6 +2171,187 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>碧丽轩 - 独立屋销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="22" t="inlineStr">
+        <is>
+          <t>5 套</t>
+        </is>
+      </c>
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="D3" s="25" t="inlineStr">
+        <is>
+          <t>5 套</t>
+        </is>
+      </c>
+      <c r="E3" s="26" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="F3" s="22" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>类型/位置</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>1号屋</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2号屋</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3号屋</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5号屋</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>6号屋</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="80" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>独立屋</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>1号屋
+4481呎 (4+房)
+(24年-07月-10日)
+$1.58亿
+$35,298/呎</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>2号屋
+4299呎 (4+房)
+(24年-01月-12日)
+$1.80亿
+$41,870/呎</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>3号屋
+4246呎 (4+房)
+(24年-06月-19日)
+$1.50亿
+$35,327/呎</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>5号屋
+5678呎 (4+房)
+(25年-02月-20日)
+$2.04亿
+$35,893/呎</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>6号屋
+3469呎 (4+房)
+(24年-06月-03日)
+$1.05亿
+$30,268/呎</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:Q6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2516,185 +2697,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>碧丽轩 - 独立屋销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="9" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="10" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="11" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="12" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="22" t="inlineStr">
-        <is>
-          <t>5 套</t>
-        </is>
-      </c>
-      <c r="B3" s="23" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="24" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="25" t="inlineStr">
-        <is>
-          <t>5 套</t>
-        </is>
-      </c>
-      <c r="E3" s="26" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="22" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>类型/位置</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>1号屋</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>2号屋</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>3号屋</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5号屋</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>6号屋</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="80" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>独立屋</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>1号屋
-4481呎 (4+房)
-(24年-07月-10日)
-$1.58亿
-$35,298/呎</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr">
-        <is>
-          <t>2号屋
-4299呎 (4+房)
-(24年-01月-12日)
-$1.80亿
-$41,870/呎</t>
-        </is>
-      </c>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t>3号屋
-4246呎 (4+房)
-(24年-06月-19日)
-$1.50亿
-$35,327/呎</t>
-        </is>
-      </c>
-      <c r="E6" s="21" t="inlineStr">
-        <is>
-          <t>5号屋
-5678呎 (4+房)
-(25年-02月-20日)
-$2.04亿
-$35,893/呎</t>
-        </is>
-      </c>
-      <c r="F6" s="21" t="inlineStr">
-        <is>
-          <t>6号屋
-3469呎 (4+房)
-(24年-06月-03日)
-$1.05亿
-$30,268/呎</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>